--- a/AAII_Financials/Quarterly/MAKSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MAKSY_QTR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Quarterly/MAKSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MAKSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>MAKSY</t>
   </si>
@@ -656,60 +656,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45655</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -737,8 +744,14 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -766,8 +779,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -795,8 +814,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -808,8 +833,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -837,8 +864,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -866,8 +899,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -895,8 +934,14 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -924,8 +969,14 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -934,8 +985,10 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -963,8 +1016,14 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -992,8 +1051,14 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1005,8 +1070,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1034,8 +1101,14 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1063,8 +1136,14 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1092,8 +1171,14 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1121,8 +1206,14 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1150,8 +1241,14 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1179,8 +1276,14 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1208,8 +1311,14 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1237,8 +1346,14 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1266,8 +1381,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1295,8 +1416,14 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1324,8 +1451,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1353,8 +1486,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1382,8 +1521,14 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1411,8 +1556,14 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1440,8 +1591,14 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1469,42 +1626,54 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45655</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1516,8 +1685,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1529,269 +1700,325 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1119100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1088400</v>
+      </c>
+      <c r="F41" s="3">
         <v>829200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>781900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1291300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1302300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1011300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1053100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1321100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1286700</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>367900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>357800</v>
+      </c>
+      <c r="F42" s="3">
         <v>216700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>204400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>9600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>9700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>11000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>11400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>9200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>351500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>341800</v>
+      </c>
+      <c r="F43" s="3">
         <v>521200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>491500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>285300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>287700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>389900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>406000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>235200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>229000</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1092500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1062500</v>
+      </c>
+      <c r="F44" s="3">
         <v>1313400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1238400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>981200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>989600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1219900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1270400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>945700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>921000</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F45" s="3">
         <v>10100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>9500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>14500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>14600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>30900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>32200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>34900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3111700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3026400</v>
+      </c>
+      <c r="F46" s="3">
         <v>2890600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2725600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2719600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2742800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2663000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2773100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2666000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2596500</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>535700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>521000</v>
+      </c>
+      <c r="F47" s="3">
         <v>899100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>847800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>880000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>887600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>895500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>932500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>959800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>934800</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7001600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6809600</v>
+      </c>
+      <c r="F48" s="3">
         <v>6985400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>6586600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>6555000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6610900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>6247300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>6505700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>6437700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6269900</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>242600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>235900</v>
+      </c>
+      <c r="F49" s="3">
         <v>228100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>215100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>226700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>228600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>219000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>228100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>201800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>196500</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1819,8 +2046,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1848,37 +2081,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>297400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>289200</v>
+      </c>
+      <c r="F52" s="3">
         <v>92500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>87200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>374600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>377800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>246600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>256800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>863500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>841000</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1906,37 +2151,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11419700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>11106600</v>
+      </c>
+      <c r="F54" s="3">
         <v>11635000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10970800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>10965400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11059000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10706200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11149100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>11255200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>10961900</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1948,8 +2205,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1961,182 +2220,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1030800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1002600</v>
+      </c>
+      <c r="F57" s="3">
         <v>2858500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2695300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>962800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>971000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2613800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2721900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>991800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>966000</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>460600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>448000</v>
+      </c>
+      <c r="F58" s="3">
         <v>443200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>417900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>316200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>318900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>409300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>426200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>549300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>535000</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1150500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1118900</v>
+      </c>
+      <c r="F59" s="3">
         <v>154400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>145600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>866000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>873400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>141800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>147700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>925300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>901100</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3595600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3497000</v>
+      </c>
+      <c r="F60" s="3">
         <v>3522000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3321000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3177900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3205000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3320000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3457300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3348200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3260900</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3351200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3259300</v>
+      </c>
+      <c r="F61" s="3">
         <v>3422100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3226700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3640900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>3672000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3607900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3757100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3939000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3836400</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>212200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>206400</v>
+      </c>
+      <c r="F62" s="3">
         <v>342400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>322900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>290000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>292500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>251400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>261800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>308200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>300100</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2164,8 +2461,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2193,8 +2496,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2222,37 +2531,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7599000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7390600</v>
+      </c>
+      <c r="F66" s="3">
         <v>7572600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7140300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>7391100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7454100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>7231300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7530500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>7938700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>7731800</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2264,8 +2585,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2293,8 +2616,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2322,8 +2651,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2351,8 +2686,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2380,37 +2721,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7622900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>7413900</v>
+      </c>
+      <c r="F72" s="3">
         <v>8071000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>7610300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>7312100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>7374500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>7108200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>7402200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>7057800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>6873900</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2438,8 +2791,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2467,8 +2826,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2496,37 +2861,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3806100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3701700</v>
+      </c>
+      <c r="F76" s="3">
         <v>4068600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3836400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3575700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3606300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3470800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3614400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3311100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3224800</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2554,42 +2931,54 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45655</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2617,8 +3006,14 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2630,37 +3025,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>120600</v>
+      </c>
+      <c r="F83" s="3">
         <v>153800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>160100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>149300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>145400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>135700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>146500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>134300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>138800</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2688,8 +3091,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2717,8 +3126,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2746,8 +3161,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2775,8 +3196,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2804,37 +3231,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>593700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>577400</v>
+      </c>
+      <c r="F89" s="3">
         <v>265200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>250100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>517500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>521900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>294200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>306400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>451500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>439700</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2846,37 +3285,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-157500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-153200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-110600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-104300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-125100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-126200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-98500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-102600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-112700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-109800</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2904,8 +3351,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2933,37 +3386,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-229900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-223600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-228500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-215400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-139700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-140900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-130600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-136000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-154000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-149900</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2975,37 +3440,45 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F96" s="3">
         <v>26900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>25400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>12400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>12500</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3033,8 +3506,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3062,8 +3541,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3091,91 +3576,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-204700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-199100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-306500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-289000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-254600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-256700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-309200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-322000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-112100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-109200</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-2800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-2700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>2800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>3000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-5500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-5700</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>159100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>154700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-270500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-255100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>122300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>123400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-145900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-152000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>182600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>177800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MAKSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MAKSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
   <si>
     <t>MAKSY</t>
   </si>
@@ -656,67 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45927</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45835</v>
+      </c>
+      <c r="F7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45655</v>
       </c>
-      <c r="F7" s="2">
-        <v>45565</v>
-      </c>
-      <c r="G7" s="2">
-        <v>45473</v>
-      </c>
       <c r="H7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="I7" s="2">
+        <v>45471</v>
+      </c>
+      <c r="J7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -750,8 +758,14 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -785,8 +799,14 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -820,8 +840,14 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,8 +861,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -870,8 +898,14 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,8 +939,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -940,8 +980,14 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -975,8 +1021,14 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -987,8 +1039,10 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1022,8 +1076,14 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1057,8 +1117,14 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1072,8 +1138,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1107,8 +1175,14 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1142,8 +1216,14 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1177,8 +1257,14 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1212,8 +1298,14 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1247,8 +1339,14 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,8 +1380,14 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1317,8 +1421,14 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1352,8 +1462,14 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,8 +1503,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1544,14 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1457,8 +1585,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,8 +1626,14 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1527,8 +1667,14 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1562,8 +1708,14 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1597,8 +1749,14 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1632,48 +1790,60 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45927</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45835</v>
+      </c>
+      <c r="F38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45655</v>
       </c>
-      <c r="F38" s="2">
-        <v>45565</v>
-      </c>
-      <c r="G38" s="2">
-        <v>45473</v>
-      </c>
       <c r="H38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="I38" s="2">
+        <v>45471</v>
+      </c>
+      <c r="J38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1687,8 +1857,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1702,323 +1874,379 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1030900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1054200</v>
+      </c>
+      <c r="F41" s="3">
         <v>1119100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1088400</v>
       </c>
-      <c r="F41" s="3">
-        <v>829200</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
+        <v>829100</v>
+      </c>
+      <c r="I41" s="3">
         <v>781900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1291300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1302300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1011300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1053100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1321100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1286700</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>107100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>109600</v>
+      </c>
+      <c r="F42" s="3">
         <v>367900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>357800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>216700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>204400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>9600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>9700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>11000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>11400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>9200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>985300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1007600</v>
+      </c>
+      <c r="F43" s="3">
         <v>351500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>341800</v>
       </c>
-      <c r="F43" s="3">
-        <v>521200</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
+        <v>521100</v>
+      </c>
+      <c r="I43" s="3">
         <v>491500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>285300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>287700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>389900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>406000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>235200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>229000</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1598900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1635100</v>
+      </c>
+      <c r="F44" s="3">
         <v>1092500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1062500</v>
       </c>
-      <c r="F44" s="3">
-        <v>1313400</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
+        <v>1313100</v>
+      </c>
+      <c r="I44" s="3">
         <v>1238400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>981200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>989600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1219900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1270400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>945700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>921000</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F45" s="3">
         <v>16200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>15700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>10100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>9500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>14500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>14600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>30900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>32200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>34900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3732000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3816400</v>
+      </c>
+      <c r="F46" s="3">
         <v>3111700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3026400</v>
       </c>
-      <c r="F46" s="3">
-        <v>2890600</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
+        <v>2890100</v>
+      </c>
+      <c r="I46" s="3">
         <v>2725600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2719600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2742800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2663000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2773100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2666000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2596500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>88600</v>
+      </c>
+      <c r="F47" s="3">
         <v>535700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>521000</v>
       </c>
-      <c r="F47" s="3">
-        <v>899100</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
+        <v>898900</v>
+      </c>
+      <c r="I47" s="3">
         <v>847800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>880000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>887600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>895500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>932500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>959800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>934800</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8222900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8408900</v>
+      </c>
+      <c r="F48" s="3">
         <v>7001600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>6809600</v>
       </c>
-      <c r="F48" s="3">
-        <v>6985400</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
+        <v>6984000</v>
+      </c>
+      <c r="I48" s="3">
         <v>6586600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>6555000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>6610900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>6247300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6505700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>6437700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6269900</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1035600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1059000</v>
+      </c>
+      <c r="F49" s="3">
         <v>242600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>235900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>228100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>215100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>226700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>228600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>219000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>228100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>201800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>196500</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2280,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2087,43 +2321,55 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>18200</v>
+      </c>
+      <c r="F52" s="3">
         <v>297400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>289200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>92500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>87200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>374600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>377800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>246600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>256800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>863500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>841000</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2157,43 +2403,55 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13500400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13805900</v>
+      </c>
+      <c r="F54" s="3">
         <v>11419700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>11106600</v>
       </c>
-      <c r="F54" s="3">
-        <v>11635000</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
+        <v>11632700</v>
+      </c>
+      <c r="I54" s="3">
         <v>10970800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10965400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11059000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>10706200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11149100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>11255200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10961900</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2465,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2222,218 +2482,256 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3914100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4002700</v>
+      </c>
+      <c r="F57" s="3">
         <v>1030800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1002600</v>
       </c>
-      <c r="F57" s="3">
-        <v>2858500</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
+        <v>2857900</v>
+      </c>
+      <c r="I57" s="3">
         <v>2695300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>962800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>971000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2613800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2721900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>991800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>966000</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>541800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>554000</v>
+      </c>
+      <c r="F58" s="3">
         <v>460600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>448000</v>
       </c>
-      <c r="F58" s="3">
-        <v>443200</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>443100</v>
+      </c>
+      <c r="I58" s="3">
         <v>417900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>316200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>318900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>409300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>426200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>549300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>535000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>152700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>156200</v>
+      </c>
+      <c r="F59" s="3">
         <v>1150500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1118900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>154400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>145600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>866000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>873400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>141800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>147700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>925300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>901100</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4608600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4712900</v>
+      </c>
+      <c r="F60" s="3">
         <v>3595600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3497000</v>
       </c>
-      <c r="F60" s="3">
-        <v>3522000</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
+        <v>3521300</v>
+      </c>
+      <c r="I60" s="3">
         <v>3321000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3177900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3205000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3320000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3457300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3348200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3260900</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4010400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4101100</v>
+      </c>
+      <c r="F61" s="3">
         <v>3351200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3259300</v>
       </c>
-      <c r="F61" s="3">
-        <v>3422100</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>3421400</v>
+      </c>
+      <c r="I61" s="3">
         <v>3226700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3640900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3672000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3607900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3757100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3939000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3836400</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>293800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>300500</v>
+      </c>
+      <c r="F62" s="3">
         <v>212200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>206400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>342400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>322900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>290000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>292500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>251400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>261800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>308200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>300100</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2765,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,8 +2806,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2537,43 +2847,55 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9516300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9731600</v>
+      </c>
+      <c r="F66" s="3">
         <v>7599000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7390600</v>
       </c>
-      <c r="F66" s="3">
-        <v>7572600</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
+        <v>7571100</v>
+      </c>
+      <c r="I66" s="3">
         <v>7140300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>7391100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7454100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>7231300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>7530500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>7938700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>7731800</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2587,8 +2909,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,8 +2946,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2657,8 +2987,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2692,8 +3028,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2727,43 +3069,55 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7719200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>7893800</v>
+      </c>
+      <c r="F72" s="3">
         <v>7622900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>7413900</v>
       </c>
-      <c r="F72" s="3">
-        <v>8071000</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
+        <v>8069400</v>
+      </c>
+      <c r="I72" s="3">
         <v>7610300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>7312100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>7374500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>7108200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>7402200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>7057800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>6873900</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2797,8 +3151,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2832,8 +3192,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2867,43 +3233,55 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3755300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3840300</v>
+      </c>
+      <c r="F76" s="3">
         <v>3806100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3701700</v>
       </c>
-      <c r="F76" s="3">
-        <v>4068600</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>4067800</v>
+      </c>
+      <c r="I76" s="3">
         <v>3836400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3575700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3606300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3470800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3614400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3311100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3224800</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2937,48 +3315,60 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45927</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45835</v>
+      </c>
+      <c r="F80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45655</v>
       </c>
-      <c r="F80" s="2">
-        <v>45565</v>
-      </c>
-      <c r="G80" s="2">
-        <v>45473</v>
-      </c>
       <c r="H80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="I80" s="2">
+        <v>45471</v>
+      </c>
+      <c r="J80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44927</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3012,8 +3402,14 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3027,43 +3423,51 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>167600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>158000</v>
+      </c>
+      <c r="F83" s="3">
         <v>119500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>120600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>153800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>160100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>149300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>145400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>135700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>146500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>134300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>138800</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3097,8 +3501,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3132,8 +3542,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3167,8 +3583,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,8 +3624,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3237,43 +3665,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>111100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>113600</v>
+      </c>
+      <c r="F89" s="3">
         <v>593700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>577400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>265200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>250100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>517500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>521900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>294200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>306400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>451500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>439700</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3287,43 +3727,51 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-111200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-113700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-157500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-153200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-110600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-104300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-125100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-126200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-98500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-102600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-112700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-109800</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3357,8 +3805,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3392,43 +3846,55 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>67500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-229900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-223600</v>
       </c>
-      <c r="F94" s="3">
-        <v>-228500</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-228400</v>
+      </c>
+      <c r="I94" s="3">
         <v>-215400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-139700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-140900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-130600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-136000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-154000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-149900</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3442,43 +3908,51 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>35900</v>
+      </c>
+      <c r="F96" s="3">
         <v>13100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>12800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>26900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>25400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>12400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>12500</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3512,8 +3986,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +4027,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3582,109 +4068,133 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-240400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-245800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-204700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-199100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-306500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-289000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-254600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-256700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-309200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-322000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-112100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-109200</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-2800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-2700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>2800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-5500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-5700</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-64200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-65700</v>
+      </c>
+      <c r="F102" s="3">
         <v>159100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>154700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-270500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-255100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>122300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>123400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-145900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-152000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>182600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>177800</v>
       </c>
     </row>
